--- a/artfynd/A 60889-2025 artfynd.xlsx
+++ b/artfynd/A 60889-2025 artfynd.xlsx
@@ -675,43 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2216792</v>
+        <v>1372074</v>
       </c>
       <c r="B2" t="n">
-        <v>108193</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219711</v>
+        <v>4366</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>653675.6368604186</v>
+        <v>653675</v>
       </c>
       <c r="R2" t="n">
-        <v>6678417.944909784</v>
+        <v>6678423</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,24 +748,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridda ex.</t>
+          <t>Enstaka ex</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,7 +769,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Blandskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -806,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1736743</v>
+        <v>1719991</v>
       </c>
       <c r="B3" t="n">
-        <v>90673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92928</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,24 +802,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5964</v>
+        <v>5836</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Guldkremla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Russula aurea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Pers.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -851,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>653675.6368604186</v>
+        <v>653674</v>
       </c>
       <c r="R3" t="n">
-        <v>6678417.944909784</v>
+        <v>6678449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,24 +868,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Enstaka ex</t>
+          <t>1 ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,44 +911,35 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1719991</v>
+        <v>1736743</v>
       </c>
       <c r="B4" t="n">
-        <v>90365</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5836</v>
+        <v>5964</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Guldkremla</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Russula aurea</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
@@ -986,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>653674.3211581002</v>
+        <v>653676</v>
       </c>
       <c r="R4" t="n">
-        <v>6678449.237246701</v>
+        <v>6678418</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,24 +984,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1 ex.</t>
+          <t>Enstaka ex</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1072,43 +1027,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1372074</v>
+        <v>2216792</v>
       </c>
       <c r="B5" t="n">
-        <v>90664</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111390</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>219711</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1117,10 +1067,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>653675.4280182773</v>
+        <v>653676</v>
       </c>
       <c r="R5" t="n">
-        <v>6678422.911965232</v>
+        <v>6678418</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,24 +1100,14 @@
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2006-10-07</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Enstaka ex</t>
+          <t>Spridda ex.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1181,7 +1121,7 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>

--- a/artfynd/A 60889-2025 artfynd.xlsx
+++ b/artfynd/A 60889-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1372074</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1719991</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1024,6 +1039,11 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1736743</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,8 +1160,19 @@
           <t>Uppföljning av skyddade områden</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2216792</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>